--- a/output/pdf_financials_xlsx/HMT.xlsx
+++ b/output/pdf_financials_xlsx/HMT.xlsx
@@ -2070,25 +2070,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>8.7e-05</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000264</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003582</v>
       </c>
     </row>
     <row r="35">
@@ -2150,25 +2150,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>8.7e-05</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000264</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003582</v>
       </c>
     </row>
     <row r="37">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
